--- a/Vulnerability_Security_Test_Report.xlsx
+++ b/Vulnerability_Security_Test_Report.xlsx
@@ -45,7 +45,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20T08:05:48.219Z</t>
+    <t>2026-08-20T08:19:48.920Z</t>
   </si>
   <si>
     <t/>
@@ -468,7 +468,7 @@
     <t>Execution Start Time</t>
   </si>
   <si>
-    <t>20/8/2026, 1:35:48 pm</t>
+    <t>20/8/2026, 1:49:48 pm</t>
   </si>
   <si>
     <t>Total Vulnerability Tests</t>
@@ -915,7 +915,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -1007,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -1030,7 +1030,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -1053,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -1099,7 +1099,7 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -1145,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
@@ -1283,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>10</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
         <v>10</v>
@@ -1398,7 +1398,7 @@
         <v>9</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -1421,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -1444,7 +1444,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -1467,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -1513,7 +1513,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
         <v>10</v>
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -1605,7 +1605,7 @@
         <v>9</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
         <v>10</v>
@@ -1628,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
@@ -1651,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -1720,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>9</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -1812,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -1835,7 +1835,7 @@
         <v>9</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>9</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -1904,7 +1904,7 @@
         <v>9</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="E46">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -1950,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -1973,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F49" t="s">
         <v>10</v>
@@ -2019,7 +2019,7 @@
         <v>9</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -2042,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
         <v>10</v>
@@ -2065,7 +2065,7 @@
         <v>9</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
         <v>10</v>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F53" t="s">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="E54">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
@@ -2134,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -2157,7 +2157,7 @@
         <v>9</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
         <v>10</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
@@ -2203,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="E58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
         <v>10</v>
@@ -2226,7 +2226,7 @@
         <v>9</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F59" t="s">
         <v>10</v>
@@ -2249,7 +2249,7 @@
         <v>9</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F60" t="s">
         <v>10</v>
@@ -2272,7 +2272,7 @@
         <v>9</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F61" t="s">
         <v>10</v>
@@ -2295,7 +2295,7 @@
         <v>9</v>
       </c>
       <c r="E62">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F62" t="s">
         <v>10</v>
@@ -2318,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="E63">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F63" t="s">
         <v>10</v>
@@ -2341,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="E64">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
@@ -2364,7 +2364,7 @@
         <v>9</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F65" t="s">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>9</v>
       </c>
       <c r="E66">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
@@ -2410,7 +2410,7 @@
         <v>9</v>
       </c>
       <c r="E67">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F67" t="s">
         <v>10</v>
@@ -2433,7 +2433,7 @@
         <v>9</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" t="s">
         <v>10</v>
@@ -2456,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="E69">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F69" t="s">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>9</v>
       </c>
       <c r="E70">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F70" t="s">
         <v>10</v>
@@ -2502,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="E71">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="E73">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F73" t="s">
         <v>10</v>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
         <v>10</v>
@@ -2594,7 +2594,7 @@
         <v>9</v>
       </c>
       <c r="E75">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F75" t="s">
         <v>10</v>
@@ -2617,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="E76">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -2640,7 +2640,7 @@
         <v>9</v>
       </c>
       <c r="E77">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F77" t="s">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>9</v>
       </c>
       <c r="E78">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F78" t="s">
         <v>10</v>
@@ -2686,7 +2686,7 @@
         <v>9</v>
       </c>
       <c r="E79">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" t="s">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>9</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80" t="s">
         <v>10</v>
@@ -2732,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="E81">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F81" t="s">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s">
         <v>10</v>
@@ -2778,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="E83">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F83" t="s">
         <v>10</v>
@@ -2801,7 +2801,7 @@
         <v>9</v>
       </c>
       <c r="E84">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F84" t="s">
         <v>10</v>
@@ -2824,7 +2824,7 @@
         <v>9</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
         <v>10</v>
@@ -2847,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="E86">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" t="s">
         <v>10</v>
@@ -2870,7 +2870,7 @@
         <v>9</v>
       </c>
       <c r="E87">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F87" t="s">
         <v>10</v>
@@ -2893,7 +2893,7 @@
         <v>9</v>
       </c>
       <c r="E88">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F88" t="s">
         <v>10</v>
@@ -2916,7 +2916,7 @@
         <v>9</v>
       </c>
       <c r="E89">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F89" t="s">
         <v>10</v>
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="E90">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" t="s">
         <v>10</v>
@@ -2962,7 +2962,7 @@
         <v>9</v>
       </c>
       <c r="E91">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F91" t="s">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>9</v>
       </c>
       <c r="E92">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F92" t="s">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>9</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F93" t="s">
         <v>10</v>
@@ -3031,7 +3031,7 @@
         <v>9</v>
       </c>
       <c r="E94">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F95" t="s">
         <v>10</v>
@@ -3077,7 +3077,7 @@
         <v>9</v>
       </c>
       <c r="E96">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F96" t="s">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>9</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F97" t="s">
         <v>10</v>
@@ -3123,7 +3123,7 @@
         <v>9</v>
       </c>
       <c r="E98">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
         <v>10</v>
@@ -3146,7 +3146,7 @@
         <v>9</v>
       </c>
       <c r="E99">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" t="s">
         <v>10</v>
@@ -3192,7 +3192,7 @@
         <v>9</v>
       </c>
       <c r="E101">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F101" t="s">
         <v>10</v>
@@ -3215,7 +3215,7 @@
         <v>9</v>
       </c>
       <c r="E102">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F102" t="s">
         <v>10</v>
@@ -3238,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="E103">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F103" t="s">
         <v>10</v>
@@ -3261,7 +3261,7 @@
         <v>9</v>
       </c>
       <c r="E104">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F104" t="s">
         <v>10</v>
@@ -3284,7 +3284,7 @@
         <v>9</v>
       </c>
       <c r="E105">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="s">
         <v>10</v>
@@ -3307,7 +3307,7 @@
         <v>9</v>
       </c>
       <c r="E106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F106" t="s">
         <v>10</v>
@@ -3330,7 +3330,7 @@
         <v>9</v>
       </c>
       <c r="E107">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
@@ -3353,7 +3353,7 @@
         <v>9</v>
       </c>
       <c r="E108">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F108" t="s">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>9</v>
       </c>
       <c r="E109">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>9</v>
       </c>
       <c r="E110">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -3422,7 +3422,7 @@
         <v>9</v>
       </c>
       <c r="E111">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F111" t="s">
         <v>10</v>
@@ -3445,7 +3445,7 @@
         <v>9</v>
       </c>
       <c r="E112">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>10</v>
@@ -3468,7 +3468,7 @@
         <v>9</v>
       </c>
       <c r="E113">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F113" t="s">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>9</v>
       </c>
       <c r="E114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F114" t="s">
         <v>10</v>
@@ -3514,7 +3514,7 @@
         <v>9</v>
       </c>
       <c r="E115">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F115" t="s">
         <v>10</v>
@@ -3537,7 +3537,7 @@
         <v>9</v>
       </c>
       <c r="E116">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F116" t="s">
         <v>10</v>
@@ -3606,7 +3606,7 @@
         <v>9</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -3629,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="E120">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
